--- a/93/food/2026-02-18-sm.xlsx
+++ b/93/food/2026-02-18-sm.xlsx
@@ -927,7 +927,7 @@
           <t>Завтрак</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>гор.блюдо</t>
         </is>
@@ -1133,7 +1133,7 @@
           <t>Обед</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>закуска</t>
         </is>
